--- a/research/files/bc_transit_stops.xlsx
+++ b/research/files/bc_transit_stops.xlsx
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Published 2026-09-02 by BC Cycle Tourism Society.</t>
+          <t>Published 2026-10-08 by BC Cycle Tourism Society.</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Suggested citation: BC Cycle Tourism Society (2026). British Columbia transit stops, in order, with locations [data set]. Version 2026-09-02. https://bccycletourism.ca/research/</t>
+          <t>Suggested citation: BC Cycle Tourism Society (2026). British Columbia transit stops, in order, with locations [data set]. Version 2026-10-08. https://bccycletourism.ca/research/</t>
         </is>
       </c>
     </row>

--- a/research/files/bc_transit_stops.xlsx
+++ b/research/files/bc_transit_stops.xlsx
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Published 2026-10-18 by BC Cycle Tourism Society.</t>
+          <t>Published 2026-10-20 by BC Cycle Tourism Society.</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Suggested citation: BC Cycle Tourism Society (2026). British Columbia transit stops, in order, with locations [data set]. Version 2026-10-18. https://bccycletourism.ca/research/</t>
+          <t>Suggested citation: BC Cycle Tourism Society (2026). British Columbia transit stops, in order, with locations [data set]. Version 2026-10-20. https://bccycletourism.ca/research/</t>
         </is>
       </c>
     </row>
